--- a/outputs/public/tables/medical_terminology/validated_clinical_terminology_summary.xlsx
+++ b/outputs/public/tables/medical_terminology/validated_clinical_terminology_summary.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/Users/sayegh-jodehl/Documents/Publikationen/Korpusanalyse_JMIR/Code_KorpusAnalyse/outputs/confidential/cleaned_corpus_tables/D_utterances_clean_lexical.csv</t>
+          <t>/Users/sayegh-jodehl/Library/Mobile Documents/com~apple~CloudDocs/Documents/Dokumente – MacBook Pro von Sabine/Publikationen/Korpusanalyse_JMIR/DocTalk-Corpus-Analysis-final/outputs/confidential/cleaned_corpus_tables/D_utterances_clean_lexical.csv</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/Users/sayegh-jodehl/Documents/Publikationen/Korpusanalyse_JMIR/Code_KorpusAnalyse/outputs/confidential/cleaned_corpus_tables/G_utterances_clean_lexical.csv</t>
+          <t>/Users/sayegh-jodehl/Library/Mobile Documents/com~apple~CloudDocs/Documents/Dokumente – MacBook Pro von Sabine/Publikationen/Korpusanalyse_JMIR/DocTalk-Corpus-Analysis-final/outputs/confidential/cleaned_corpus_tables/G_utterances_clean_lexical.csv</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -667,10 +667,10 @@
         <v>4154</v>
       </c>
       <c r="D2" t="n">
-        <v>3283</v>
+        <v>3279</v>
       </c>
       <c r="E2" t="n">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5919753702022805</v>
+        <v>0.5931159778519959</v>
       </c>
     </row>
     <row r="3">
@@ -783,10 +783,10 @@
         <v>90297</v>
       </c>
       <c r="D3" t="n">
-        <v>2080</v>
+        <v>2076</v>
       </c>
       <c r="E3" t="n">
-        <v>23.03509529663222</v>
+        <v>22.99079703644639</v>
       </c>
       <c r="F3" t="n">
         <v>765</v>
@@ -798,7 +798,7 @@
         <v>493</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5919753702022805</v>
+        <v>0.5931159778519959</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
         <v>90297</v>
       </c>
       <c r="E7" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F7" t="n">
-        <v>5.448686002857238</v>
+        <v>5.459760567903696</v>
       </c>
       <c r="G7" t="n">
         <v>228</v>
@@ -1063,7 +1063,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medikation</t>
+          <t>procedure</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1078,25 +1078,25 @@
         <v>88221</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.777116559549313</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3.634878497039003</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>medikation</t>
+          <t>procedure</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,25 +1111,25 @@
         <v>90297</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>319</v>
       </c>
       <c r="F9" t="n">
-        <v>0.055372825232289</v>
+        <v>3.532786249820038</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>229</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1964636542239686</v>
+        <v>8.99803536345776</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>procedure</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1144,25 +1144,25 @@
         <v>88221</v>
       </c>
       <c r="E10" t="n">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="F10" t="n">
-        <v>2.777116559549313</v>
+        <v>2.459731809886535</v>
       </c>
       <c r="G10" t="n">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="H10" t="n">
-        <v>3.634878497039003</v>
+        <v>3.144782519910149</v>
       </c>
       <c r="I10" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>procedure</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1177,25 +1177,25 @@
         <v>90297</v>
       </c>
       <c r="E11" t="n">
-        <v>319</v>
+        <v>586</v>
       </c>
       <c r="F11" t="n">
-        <v>3.532786249820038</v>
+        <v>6.489695117224271</v>
       </c>
       <c r="G11" t="n">
-        <v>229</v>
+        <v>373</v>
       </c>
       <c r="H11" t="n">
-        <v>8.99803536345776</v>
+        <v>14.65618860510806</v>
       </c>
       <c r="I11" t="n">
-        <v>78</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>symptom</t>
+          <t>therapy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1210,25 +1210,25 @@
         <v>88221</v>
       </c>
       <c r="E12" t="n">
-        <v>217</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
-        <v>2.459731809886535</v>
+        <v>1.201527980866234</v>
       </c>
       <c r="G12" t="n">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="H12" t="n">
-        <v>3.144782519910149</v>
+        <v>2.103328568511333</v>
       </c>
       <c r="I12" t="n">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>symptom</t>
+          <t>therapy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1243,25 +1243,25 @@
         <v>90297</v>
       </c>
       <c r="E13" t="n">
-        <v>586</v>
+        <v>144</v>
       </c>
       <c r="F13" t="n">
-        <v>6.489695117224271</v>
+        <v>1.594737366689923</v>
       </c>
       <c r="G13" t="n">
-        <v>373</v>
+        <v>130</v>
       </c>
       <c r="H13" t="n">
-        <v>14.65618860510806</v>
+        <v>5.108055009823183</v>
       </c>
       <c r="I13" t="n">
-        <v>142</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>therapy</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1276,25 +1276,25 @@
         <v>88221</v>
       </c>
       <c r="E14" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="F14" t="n">
-        <v>1.201527980866234</v>
+        <v>0.6007639904331169</v>
       </c>
       <c r="G14" t="n">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="H14" t="n">
-        <v>2.103328568511333</v>
+        <v>1.061874617112518</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>therapy</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1309,84 +1309,18 @@
         <v>90297</v>
       </c>
       <c r="E15" t="n">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>1.594737366689923</v>
+        <v>0.7641449882055882</v>
       </c>
       <c r="G15" t="n">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="H15" t="n">
-        <v>5.108055009823183</v>
+        <v>2.396856581532417</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4897</v>
-      </c>
-      <c r="D16" t="n">
-        <v>88221</v>
-      </c>
-      <c r="E16" t="n">
-        <v>53</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.6007639904331169</v>
-      </c>
-      <c r="G16" t="n">
-        <v>52</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.061874617112518</v>
-      </c>
-      <c r="I16" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2545</v>
-      </c>
-      <c r="D17" t="n">
-        <v>90297</v>
-      </c>
-      <c r="E17" t="n">
-        <v>69</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.7641449882055882</v>
-      </c>
-      <c r="G17" t="n">
-        <v>61</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2.396856581532417</v>
-      </c>
-      <c r="I17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1401,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1474,344 +1408,301 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>medikation</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.6007639904331169</v>
       </c>
       <c r="E2" t="n">
-        <v>0.055372825232289</v>
+        <v>0.7641449882055882</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.055372825232289</v>
+        <v>-0.1633809977724713</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.7861911020889734</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1.061874617112518</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1964636542239686</v>
+        <v>2.396856581532417</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>treatment</t>
+          <t>clinical_risk</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6007639904331169</v>
+        <v>0.1926978837238299</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7641449882055882</v>
+        <v>0.4651317319512276</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1633809977724713</v>
+        <v>-0.2724338482273977</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7861911020889734</v>
+        <v>0.4142866858716826</v>
       </c>
       <c r="H3" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="J3" t="n">
-        <v>1.061874617112518</v>
+        <v>0.3267306514192362</v>
       </c>
       <c r="K3" t="n">
-        <v>2.396856581532417</v>
+        <v>1.453831041257367</v>
       </c>
       <c r="L3" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>clinical_risk</t>
+          <t>therapy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1926978837238299</v>
+        <v>1.201527980866234</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4651317319512276</v>
+        <v>1.594737366689923</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2724338482273977</v>
+        <v>-0.3932093858236894</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4142866858716826</v>
+        <v>0.7534331395019328</v>
       </c>
       <c r="H4" t="n">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3267306514192362</v>
+        <v>2.103328568511333</v>
       </c>
       <c r="K4" t="n">
-        <v>1.453831041257367</v>
+        <v>5.108055009823183</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>therapy</t>
+          <t>procedure</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="C5" t="n">
-        <v>144</v>
+        <v>319</v>
       </c>
       <c r="D5" t="n">
-        <v>1.201527980866234</v>
+        <v>2.777116559549313</v>
       </c>
       <c r="E5" t="n">
-        <v>1.594737366689923</v>
+        <v>3.532786249820038</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3932093858236894</v>
+        <v>-0.7556696902707247</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7534331395019328</v>
+        <v>0.7860981002433366</v>
       </c>
       <c r="H5" t="n">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="I5" t="n">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="J5" t="n">
-        <v>2.103328568511333</v>
+        <v>3.634878497039003</v>
       </c>
       <c r="K5" t="n">
-        <v>5.108055009823183</v>
+        <v>8.99803536345776</v>
       </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="M5" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>procedure</t>
+          <t>diagnosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>319</v>
+        <v>423</v>
       </c>
       <c r="D6" t="n">
-        <v>2.777116559549313</v>
+        <v>2.833792407703382</v>
       </c>
       <c r="E6" t="n">
-        <v>3.532786249820038</v>
+        <v>4.684541014651649</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7556696902707247</v>
+        <v>-1.850748606948267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7860981002433366</v>
+        <v>0.6049242388614474</v>
       </c>
       <c r="H6" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I6" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="J6" t="n">
-        <v>3.634878497039003</v>
+        <v>3.51235450275679</v>
       </c>
       <c r="K6" t="n">
-        <v>8.99803536345776</v>
+        <v>9.155206286836934</v>
       </c>
       <c r="L6" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="M6" t="n">
-        <v>78</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>medication</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>423</v>
+        <v>493</v>
       </c>
       <c r="D7" t="n">
-        <v>2.833792407703382</v>
+        <v>3.57057843370626</v>
       </c>
       <c r="E7" t="n">
-        <v>4.684541014651649</v>
+        <v>5.459760567903696</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.850748606948267</v>
+        <v>-1.889182134197435</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6049242388614474</v>
+        <v>0.6539807724713472</v>
       </c>
       <c r="H7" t="n">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="I7" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J7" t="n">
-        <v>3.51235450275679</v>
+        <v>4.308760465591178</v>
       </c>
       <c r="K7" t="n">
-        <v>9.155206286836934</v>
+        <v>8.958742632612966</v>
       </c>
       <c r="L7" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="M7" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medication</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>315</v>
+        <v>217</v>
       </c>
       <c r="C8" t="n">
-        <v>492</v>
+        <v>586</v>
       </c>
       <c r="D8" t="n">
-        <v>3.57057843370626</v>
+        <v>2.459731809886535</v>
       </c>
       <c r="E8" t="n">
-        <v>5.448686002857238</v>
+        <v>6.489695117224271</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.878107569150978</v>
+        <v>-4.029963307337736</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6553100016836874</v>
+        <v>0.3790211659340008</v>
       </c>
       <c r="H8" t="n">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="I8" t="n">
-        <v>228</v>
+        <v>373</v>
       </c>
       <c r="J8" t="n">
-        <v>4.308760465591178</v>
+        <v>3.144782519910149</v>
       </c>
       <c r="K8" t="n">
-        <v>8.958742632612966</v>
+        <v>14.65618860510806</v>
       </c>
       <c r="L8" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="M8" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>symptom</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>217</v>
-      </c>
-      <c r="C9" t="n">
-        <v>586</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.459731809886535</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6.489695117224271</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-4.029963307337736</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.3790211659340008</v>
-      </c>
-      <c r="H9" t="n">
-        <v>154</v>
-      </c>
-      <c r="I9" t="n">
-        <v>373</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.144782519910149</v>
-      </c>
-      <c r="K9" t="n">
-        <v>14.65618860510806</v>
-      </c>
-      <c r="L9" t="n">
-        <v>86</v>
-      </c>
-      <c r="M9" t="n">
         <v>142</v>
       </c>
     </row>
@@ -1826,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K314"/>
+  <dimension ref="A1:K313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6169,7 +6060,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Infliximab</t>
+          <t>Ibuprophen</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -6179,30 +6070,30 @@
         <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Infliximab</t>
+          <t>Ibupro; Ibuprofen; ibu</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex; medner</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6105,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Magensonde</t>
+          <t>Infliximab</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -6224,16 +6115,16 @@
         <v>7</v>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6242,7 +6133,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Magensonde</t>
+          <t>Infliximab</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6259,7 +6150,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Olanzapin</t>
+          <t>Magensonde</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -6269,16 +6160,16 @@
         <v>7</v>
       </c>
       <c r="E99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6287,12 +6178,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Antidepressiva; Olanzapin; olanzapin</t>
+          <t>Magensonde</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6195,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SSRI</t>
+          <t>Olanzapin</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6314,16 +6205,16 @@
         <v>7</v>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H100" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6332,12 +6223,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>SSRI</t>
+          <t>Antidepressiva; Olanzapin; olanzapin</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>gliner; humadex; medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6240,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Schmerzmedikation</t>
+          <t>SSRI</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -6359,30 +6250,30 @@
         <v>7</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Schmerzed; Schmerzmed</t>
+          <t>SSRI</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner; humadex; medner</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6285,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sirdalut</t>
+          <t>Schmerzmedikation</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -6422,7 +6313,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Sirdalud</t>
+          <t>Schmerzed; Schmerzmed</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6439,35 +6330,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Amitriptylin</t>
+          <t>Sirdalut</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Amitriptylin; amitryptilin</t>
+          <t>Sirdalud</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6484,7 +6375,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fosfomycin</t>
+          <t>Amitriptylin</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -6494,25 +6385,25 @@
         <v>6</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Fosfomy; Fosfomycin</t>
+          <t>Amitriptylin; amitryptilin</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6529,7 +6420,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ibuprophen</t>
+          <t>Fosfomycin</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -6557,12 +6448,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Ibupro; Ibuprofen; ibu</t>
+          <t>Fosfomy; Fosfomycin</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>humadex; medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -8234,45 +8125,45 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>medikation</t>
+          <t>procedure</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ibuprophen</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F143" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H143" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Ibuprofen</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -8284,26 +8175,26 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>EKG</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D144" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E144" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F144" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G144" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H144" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -8312,12 +8203,12 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>EKG; ekg; pu; sweat</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -8329,27 +8220,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EKG</t>
+          <t>PCR Test</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D145" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E145" t="n">
+        <v>14</v>
+      </c>
+      <c r="F145" t="n">
         <v>17</v>
       </c>
-      <c r="F145" t="n">
-        <v>22</v>
-      </c>
       <c r="G145" t="n">
+        <v>14</v>
+      </c>
+      <c r="H145" t="n">
         <v>17</v>
       </c>
-      <c r="H145" t="n">
-        <v>22</v>
-      </c>
       <c r="I145" t="inlineStr">
         <is>
           <t>direct_and_group</t>
@@ -8357,12 +8248,12 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>EKG; ekg; pu; sweat</t>
+          <t>PCR; italopram; pcrTest</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner; humadex; medner</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8265,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PCR Test</t>
+          <t>Therapie</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -8384,16 +8275,16 @@
         <v>31</v>
       </c>
       <c r="E146" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F146" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G146" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H146" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -8402,12 +8293,12 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>PCR; italopram; pcrTest</t>
+          <t>Therapie</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>gliner; humadex; medner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -8419,26 +8310,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Therapie</t>
+          <t>Blutentnahme (BE)</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D147" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E147" t="n">
         <v>11</v>
       </c>
       <c r="F147" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G147" t="n">
         <v>11</v>
       </c>
       <c r="H147" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -8447,12 +8338,12 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Therapie</t>
+          <t>BE; Be; Blutent; Blutentnahmen</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex; medner</t>
         </is>
       </c>
     </row>
@@ -8464,26 +8355,26 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Blutentnahme (BE)</t>
+          <t>Operation (OP)</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D148" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E148" t="n">
         <v>11</v>
       </c>
       <c r="F148" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G148" t="n">
         <v>11</v>
       </c>
       <c r="H148" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -8492,7 +8383,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>BE; Be; Blutent; Blutentnahmen</t>
+          <t>OP; Op; Operation</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8509,26 +8400,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Operation (OP)</t>
+          <t>Behandlung</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D149" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E149" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G149" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -8537,12 +8428,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>OP; Op; Operation</t>
+          <t>Behandlung</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>gliner; humadex; medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -8554,26 +8445,26 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Behandlung</t>
+          <t>Dermatologisches Konsil</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D150" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E150" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F150" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G150" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H150" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -8582,7 +8473,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Behandlung</t>
+          <t>Derma Konsil; Dermakon; Dermakonsil; Hautkonsil</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -8599,26 +8490,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dermatologisches Konsil</t>
+          <t>Natrium (Na+)</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D151" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E151" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F151" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G151" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H151" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -8627,12 +8518,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Derma Konsil; Dermakon; Dermakonsil; Hautkonsil</t>
+          <t>Na; Natrium</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner; humadex; medner</t>
         </is>
       </c>
     </row>
@@ -8644,23 +8535,23 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Natrium (Na+)</t>
+          <t>Computertomographie (CT)</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D152" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F152" t="n">
         <v>7</v>
       </c>
       <c r="G152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H152" t="n">
         <v>7</v>
@@ -8672,7 +8563,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Na; Natrium</t>
+          <t>CT; ct</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -8689,7 +8580,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Computertomographie (CT)</t>
+          <t>Lebertransplantation</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -8699,16 +8590,16 @@
         <v>12</v>
       </c>
       <c r="E153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G153" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H153" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -8717,12 +8608,12 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>CT; ct</t>
+          <t>Lebertransplantation</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>gliner; humadex; medner</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8625,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lebertransplantation</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -8744,16 +8635,16 @@
         <v>12</v>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F154" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H154" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -8762,12 +8653,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lebertransplantation</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8670,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>Schnelltest</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -8789,16 +8680,16 @@
         <v>12</v>
       </c>
       <c r="E155" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F155" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G155" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H155" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -8807,7 +8698,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>Schnelltest; Schnelltests</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -8824,27 +8715,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Schnelltest</t>
+          <t>Koloskopie</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D156" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E156" t="n">
+        <v>3</v>
+      </c>
+      <c r="F156" t="n">
         <v>7</v>
       </c>
-      <c r="F156" t="n">
-        <v>5</v>
-      </c>
       <c r="G156" t="n">
+        <v>3</v>
+      </c>
+      <c r="H156" t="n">
         <v>7</v>
       </c>
-      <c r="H156" t="n">
-        <v>5</v>
-      </c>
       <c r="I156" t="inlineStr">
         <is>
           <t>direct_and_group</t>
@@ -8852,7 +8743,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Schnelltest; Schnelltests</t>
+          <t>Colonoscopy; Kolo; Kolosko; Koloskopie; koloskopie</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -8869,7 +8760,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Koloskopie</t>
+          <t>Rekonsil</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -8879,16 +8770,16 @@
         <v>10</v>
       </c>
       <c r="E157" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F157" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H157" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -8897,12 +8788,12 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Colonoscopy; Kolo; Kolosko; Koloskopie; koloskopie</t>
+          <t>Rekonsil</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -8914,26 +8805,26 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Rekonsil</t>
+          <t>EEG</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D158" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -8942,7 +8833,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>Rekonsil</t>
+          <t>EEG</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -8959,7 +8850,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EEG</t>
+          <t>LTX</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -8969,25 +8860,25 @@
         <v>8</v>
       </c>
       <c r="E159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>EEG</t>
+          <t>LTX</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9004,40 +8895,40 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>LTX</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D160" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F160" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H160" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>LTX</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -9049,27 +8940,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Endoskopie</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D161" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
         <v>5</v>
       </c>
-      <c r="F161" t="n">
-        <v>2</v>
-      </c>
       <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="n">
         <v>5</v>
       </c>
-      <c r="H161" t="n">
-        <v>2</v>
-      </c>
       <c r="I161" t="inlineStr">
         <is>
           <t>direct_and_group</t>
@@ -9077,7 +8968,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Endosko; Endoskopie</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -9094,7 +8985,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Endoskopie</t>
+          <t>Entlassung</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -9122,12 +9013,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Endosko; Endoskopie</t>
+          <t>Entlassung</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -9139,35 +9030,35 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Entlassung</t>
+          <t>Aufnahmegespräch</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
         <v>5</v>
       </c>
-      <c r="G163" t="n">
-        <v>1</v>
-      </c>
       <c r="H163" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Entlassung</t>
+          <t>AUfnahmegespräch; Aufnahmegespräch</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9184,7 +9075,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Aufnahmegespräch</t>
+          <t>Phosphat</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -9194,30 +9085,30 @@
         <v>5</v>
       </c>
       <c r="E164" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" t="n">
         <v>5</v>
       </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
       <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
         <v>5</v>
       </c>
-      <c r="H164" t="n">
-        <v>0</v>
-      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>AUfnahmegespräch; Aufnahmegespräch</t>
+          <t>Phospha</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9120,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Phosphat</t>
+          <t>Röntgen</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -9239,30 +9130,30 @@
         <v>5</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H165" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Phospha</t>
+          <t>Röntgen</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9165,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Röntgen</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -9284,16 +9175,16 @@
         <v>5</v>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -9302,12 +9193,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Röntgen</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9210,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>Testosteronbestimmung</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -9329,16 +9220,16 @@
         <v>5</v>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -9347,7 +9238,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>Testosteronbestimmung</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -9364,7 +9255,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Testosteronbestimmung</t>
+          <t>ÖGD</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -9374,16 +9265,16 @@
         <v>5</v>
       </c>
       <c r="E168" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G168" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -9392,7 +9283,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Testosteronbestimmung</t>
+          <t>ÖGD</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -9409,35 +9300,35 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ÖGD</t>
+          <t>Diagnostik</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
         <v>4</v>
       </c>
       <c r="G169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
         <v>4</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>ÖGD</t>
+          <t>Diagnostik</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -9454,7 +9345,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Diagnostik</t>
+          <t>Krea</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -9464,30 +9355,30 @@
         <v>4</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H170" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Diagnostik</t>
+          <t>Kre; Krea</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9390,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Krea</t>
+          <t>Labor Kontrolle</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -9509,30 +9400,30 @@
         <v>4</v>
       </c>
       <c r="E171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G171" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Kre; Krea</t>
+          <t>Labor Kontrolle</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9435,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Labor Kontrolle</t>
+          <t>NT proBNP</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -9554,25 +9445,25 @@
         <v>4</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F172" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H172" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Labor Kontrolle</t>
+          <t>NT proBNP</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -9589,7 +9480,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>NT proBNP</t>
+          <t>OGTT</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -9599,25 +9490,25 @@
         <v>4</v>
       </c>
       <c r="E173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>NT proBNP</t>
+          <t>OGTT</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -9634,7 +9525,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>OGTT</t>
+          <t>Plasmaspiegelbestimmungen</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -9644,25 +9535,25 @@
         <v>4</v>
       </c>
       <c r="E174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>OGTT</t>
+          <t>Plasmaspiegelbestimmungen</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -9679,7 +9570,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Plasmaspiegelbestimmungen</t>
+          <t>Sono</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -9689,30 +9580,30 @@
         <v>4</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Plasmaspiegelbestimmungen</t>
+          <t>Can; Sono</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9615,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Sono</t>
+          <t>Sono Abdomen</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -9734,30 +9625,30 @@
         <v>4</v>
       </c>
       <c r="E176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Can; Sono</t>
+          <t>Sono Abdomen</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9660,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Sono Abdomen</t>
+          <t>Toxurin</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -9797,7 +9688,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Sono Abdomen</t>
+          <t>Toxurin</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -9814,7 +9705,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Toxurin</t>
+          <t>Visite</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -9824,25 +9715,25 @@
         <v>4</v>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Toxurin</t>
+          <t>Visite</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -9859,7 +9750,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Visite</t>
+          <t>cMRT</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -9869,16 +9760,16 @@
         <v>4</v>
       </c>
       <c r="E179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -9887,7 +9778,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Visite</t>
+          <t>cMRT</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -9904,26 +9795,26 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>cMRT</t>
+          <t>Albumin</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -9932,12 +9823,12 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>cMRT</t>
+          <t>Albumin</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9840,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Albumin</t>
+          <t>Ausschluss</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -9959,16 +9850,16 @@
         <v>3</v>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -9977,12 +9868,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Albumin</t>
+          <t>Ausschluss</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -9994,7 +9885,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ausschluss</t>
+          <t>Bildgebung</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -10022,12 +9913,12 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Ausschluss</t>
+          <t>Bildgebung</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -10039,7 +9930,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Bildgebung</t>
+          <t>Cholestase</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -10049,30 +9940,30 @@
         <v>3</v>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>Bildgebung</t>
+          <t>Cholestase</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -10084,7 +9975,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Cholestase</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -10094,25 +9985,25 @@
         <v>3</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Cholestase</t>
+          <t>DAN</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -10129,7 +10020,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DAN</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -10157,7 +10048,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>DAN</t>
+          <t>Echo</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -10174,7 +10065,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Ferr</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -10184,30 +10075,30 @@
         <v>3</v>
       </c>
       <c r="E186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Echo</t>
+          <t>Ferr</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>medner</t>
         </is>
       </c>
     </row>
@@ -10219,7 +10110,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ferr</t>
+          <t>Funktionellen Röntgen</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -10247,12 +10138,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Ferr</t>
+          <t>Funktionellen Röntgen</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>medner</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10155,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Funktionellen Röntgen</t>
+          <t>Herzenzyme</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -10274,25 +10165,25 @@
         <v>3</v>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Funktionellen Röntgen</t>
+          <t>Herzenzyme</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -10309,7 +10200,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Herzenzyme</t>
+          <t>Laborkontrolle</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -10319,25 +10210,25 @@
         <v>3</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Herzenzyme</t>
+          <t>Laborkontrolle</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -10354,7 +10245,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Laborkontrolle</t>
+          <t>Magnetresonanztomographie (MR)</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -10364,30 +10255,30 @@
         <v>3</v>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H190" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>Laborkontrolle</t>
+          <t>MR</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10290,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Magnetresonanztomographie (MR)</t>
+          <t>Plasmaprotein</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -10409,25 +10300,25 @@
         <v>3</v>
       </c>
       <c r="E191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>MR</t>
+          <t>Plasmaprotein</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -10444,7 +10335,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Plasmaprotein</t>
+          <t>Schmerzkonsil</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -10454,30 +10345,30 @@
         <v>3</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>Plasmaprotein</t>
+          <t>Schmerzkonsil</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -10489,7 +10380,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Schmerzkonsil</t>
+          <t>Ösophagektomie</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -10499,25 +10390,25 @@
         <v>3</v>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>Schmerzkonsil</t>
+          <t>Ösophagektomie</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -10529,45 +10420,45 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>procedure</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ösophagektomie</t>
+          <t>Tod</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="D194" t="n">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F194" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H194" t="n">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Ösophagektomie</t>
+          <t>Tod</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>medner</t>
         </is>
       </c>
     </row>
@@ -10579,26 +10470,26 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tod</t>
+          <t>Schmerzen</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="D195" t="n">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="E195" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F195" t="n">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="G195" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H195" t="n">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -10607,12 +10498,12 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Tod</t>
+          <t>Schmer; Schmerz; Schmerzen; Schmerzen beim Stehen; Schmerzen im Finger; mor; schmerzen; ziemlich starke Schmerzen</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -10624,26 +10515,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Schmerzen</t>
+          <t>Symptom</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D196" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="E196" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F196" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G196" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H196" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -10652,7 +10543,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Schmer; Schmerz; Schmerzen; Schmerzen beim Stehen; Schmerzen im Finger; mor; schmerzen; ziemlich starke Schmerzen</t>
+          <t>Symptoma; Symptome; Symptomen; Traumaerfahrung</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -10669,26 +10560,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Symptom</t>
+          <t>Gewichtszunahme</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D197" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E197" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F197" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G197" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H197" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -10697,7 +10588,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Symptoma; Symptome; Symptomen; Traumaerfahrung</t>
+          <t>CT; Gewichtszunah; Gewichtszunahme</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -10714,7 +10605,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Gewichtszunahme</t>
+          <t>Myalgien</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -10724,16 +10615,16 @@
         <v>17</v>
       </c>
       <c r="E198" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F198" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G198" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H198" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -10742,7 +10633,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>CT; Gewichtszunah; Gewichtszunahme</t>
+          <t>Muskelschmer; Muskelschmerzen; Myalgien</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -10759,7 +10650,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Myalgien</t>
+          <t>Übelkeit</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -10769,16 +10660,16 @@
         <v>17</v>
       </c>
       <c r="E199" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F199" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G199" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H199" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -10787,7 +10678,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Muskelschmer; Muskelschmerzen; Myalgien</t>
+          <t>Übelkeit</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -10804,26 +10695,26 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Übelkeit</t>
+          <t>Schwindel</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D200" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E200" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F200" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G200" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H200" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -10832,7 +10723,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Übelkeit</t>
+          <t>Schwind; Schwindel</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -10849,27 +10740,27 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Schwindel</t>
+          <t>Episode</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D201" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E201" t="n">
+        <v>9</v>
+      </c>
+      <c r="F201" t="n">
         <v>6</v>
       </c>
-      <c r="F201" t="n">
-        <v>10</v>
-      </c>
       <c r="G201" t="n">
+        <v>9</v>
+      </c>
+      <c r="H201" t="n">
         <v>6</v>
       </c>
-      <c r="H201" t="n">
-        <v>10</v>
-      </c>
       <c r="I201" t="inlineStr">
         <is>
           <t>direct_and_group</t>
@@ -10877,12 +10768,12 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Schwind; Schwindel</t>
+          <t>Episode</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -10894,26 +10785,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Episode</t>
+          <t>Erbrechen</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D202" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E202" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F202" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G202" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H202" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -10922,12 +10813,12 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Episode</t>
+          <t>Erbrechen</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -10939,7 +10830,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Erbrechen</t>
+          <t>Kopfschmerzenen</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -10949,16 +10840,16 @@
         <v>13</v>
       </c>
       <c r="E203" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F203" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G203" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H203" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -10967,7 +10858,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>Erbrechen</t>
+          <t>Kopfschmerz; Kopfschmerzen</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -10984,26 +10875,26 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Kopfschmerzenen</t>
+          <t>Anspannung</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D204" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E204" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F204" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H204" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -11012,7 +10903,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Kopfschmerz; Kopfschmerzen</t>
+          <t>Anspannu; Anspannung</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -11029,7 +10920,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Anspannung</t>
+          <t>Schmerzedukation</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -11039,16 +10930,16 @@
         <v>12</v>
       </c>
       <c r="E205" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F205" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G205" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H205" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -11057,12 +10948,12 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Anspannu; Anspannung</t>
+          <t>Schmerzedukation</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -11074,26 +10965,26 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Schmerzedukation</t>
+          <t>Angst</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D206" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E206" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G206" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -11102,12 +10993,12 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>Schmerzedukation</t>
+          <t>Angst; Angst Angstkreislauf; Ängste</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -11119,26 +11010,26 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Angst</t>
+          <t>Erschöpfung</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D207" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E207" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G207" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H207" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -11147,12 +11038,12 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Angst; Angst Angstkreislauf; Ängste</t>
+          <t>Erschöpfung; Erschöpfungs</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11055,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Erschöpfung</t>
+          <t>Tachykardie</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -11192,7 +11083,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Erschöpfung; Erschöpfungs</t>
+          <t>Tachykardie; Tachykardien</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -11209,7 +11100,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tachykardie</t>
+          <t>Wut</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -11219,16 +11110,16 @@
         <v>10</v>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F209" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H209" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -11237,7 +11128,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>Tachykardie; Tachykardien</t>
+          <t>Wut</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -11254,26 +11145,26 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Wut</t>
+          <t>Schlaf</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E210" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G210" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H210" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -11282,12 +11173,12 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Wut</t>
+          <t>Schlaf</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11190,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Schlaf</t>
+          <t>Stress</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -11309,16 +11200,16 @@
         <v>9</v>
       </c>
       <c r="E211" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F211" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G211" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H211" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -11327,12 +11218,12 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Schlaf</t>
+          <t>Stress</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -11344,27 +11235,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Stress</t>
+          <t>Angstsymptome</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E212" t="n">
+        <v>3</v>
+      </c>
+      <c r="F212" t="n">
         <v>5</v>
       </c>
-      <c r="F212" t="n">
-        <v>4</v>
-      </c>
       <c r="G212" t="n">
+        <v>3</v>
+      </c>
+      <c r="H212" t="n">
         <v>5</v>
       </c>
-      <c r="H212" t="n">
-        <v>4</v>
-      </c>
       <c r="I212" t="inlineStr">
         <is>
           <t>direct_and_group</t>
@@ -11372,7 +11263,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>Stress</t>
+          <t>Angstsymptomatik; Angstsymptome</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -11389,7 +11280,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Angstsymptome</t>
+          <t>Bauchschmerzen</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -11399,16 +11290,16 @@
         <v>8</v>
       </c>
       <c r="E213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H213" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -11417,7 +11308,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>Angstsymptomatik; Angstsymptome</t>
+          <t>Bauchschmerzen; Bauschmerzen</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -11434,7 +11325,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Bauchschmerzen</t>
+          <t>Gewichtsverlust</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -11444,16 +11335,16 @@
         <v>8</v>
       </c>
       <c r="E214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F214" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G214" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H214" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -11462,7 +11353,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>Bauchschmerzen; Bauschmerzen</t>
+          <t>Gewichtsabnahme; Gewichtsverlust</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -11479,7 +11370,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Gewichtsverlust</t>
+          <t>Tacrolimus Spiegel</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -11489,30 +11380,30 @@
         <v>8</v>
       </c>
       <c r="E215" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G215" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>Gewichtsabnahme; Gewichtsverlust</t>
+          <t>Tac Spiegel</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11415,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tacrolimus Spiegel</t>
+          <t>innerer Anspannung</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -11534,25 +11425,25 @@
         <v>8</v>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F216" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H216" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>Tac Spiegel</t>
+          <t>innere Anspannung; innerer Anspannung</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -11569,26 +11460,26 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>innerer Anspannung</t>
+          <t>Bewegungsdrang</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D217" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E217" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G217" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -11597,7 +11488,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>innere Anspannung; innerer Anspannung</t>
+          <t>Bewegungsdrang</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -11614,7 +11505,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Bewegungsdrang</t>
+          <t>Blutdruck (RR)</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -11624,16 +11515,16 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -11642,12 +11533,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Bewegungsdrang</t>
+          <t>Blutdr; Blutdruck; RR</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11550,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Blutdruck (RR)</t>
+          <t>Dyspnoe</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -11669,16 +11560,16 @@
         <v>7</v>
       </c>
       <c r="E219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G219" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -11687,7 +11578,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Blutdr; Blutdruck; RR</t>
+          <t>Dypnoe; Dyspnoe</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -11704,7 +11595,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Dyspnoe</t>
+          <t>Frustration</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -11714,16 +11605,16 @@
         <v>7</v>
       </c>
       <c r="E220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H220" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -11732,12 +11623,12 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>Dypnoe; Dyspnoe</t>
+          <t>Frustration</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -11749,7 +11640,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Frustration</t>
+          <t>Heimweh</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -11777,7 +11668,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Frustration</t>
+          <t>Heimweh</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -11794,26 +11685,26 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Heimweh</t>
+          <t>Brustschmerz</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D222" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F222" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H222" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -11822,12 +11713,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Heimweh</t>
+          <t>Brustschmerz; Sartan</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11730,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Brustschmerz</t>
+          <t>Bulimia nervosa (BN)</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -11849,30 +11740,30 @@
         <v>6</v>
       </c>
       <c r="E223" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F223" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H223" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Brustschmerz; Sartan</t>
+          <t>Bulimie</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11775,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Bulimia nervosa (BN)</t>
+          <t>Dilatation</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -11894,25 +11785,25 @@
         <v>6</v>
       </c>
       <c r="E224" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" t="n">
         <v>6</v>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
       <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
         <v>6</v>
       </c>
-      <c r="H224" t="n">
-        <v>0</v>
-      </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Bulimie</t>
+          <t>Dilatation</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -11929,7 +11820,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Dilatation</t>
+          <t>Entzündung</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -11957,12 +11848,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>Dilatation</t>
+          <t>Entzünd; Entzündung</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11865,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Entzündung</t>
+          <t>Traurigkeit</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -11984,30 +11875,30 @@
         <v>6</v>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F226" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H226" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Entzünd; Entzündung</t>
+          <t>Traurigkeit</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -12019,35 +11910,35 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Traurigkeit</t>
+          <t>Antriebslosigkeit</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D227" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>Traurigkeit</t>
+          <t>Antriebslosigkeit</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -12064,7 +11955,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Antriebslosigkeit</t>
+          <t>Beinödeme</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -12074,30 +11965,30 @@
         <v>5</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F228" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H228" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Antriebslosigkeit</t>
+          <t>Beinödeme</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12000,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Beinödeme</t>
+          <t>CRP</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -12137,12 +12028,12 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>Beinödeme</t>
+          <t>CRP</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12045,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>CRP</t>
+          <t>Depression</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -12164,16 +12055,16 @@
         <v>5</v>
       </c>
       <c r="E230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H230" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -12182,12 +12073,12 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>CRP</t>
+          <t>depress</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -12199,7 +12090,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Depression</t>
+          <t>Essanfälle</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -12209,16 +12100,16 @@
         <v>5</v>
       </c>
       <c r="E231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -12227,12 +12118,12 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>depress</t>
+          <t>Essanfälle</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12135,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Essanfälle</t>
+          <t>Fatigue</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -12254,25 +12145,25 @@
         <v>5</v>
       </c>
       <c r="E232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>Essanfälle</t>
+          <t>Fatigue</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -12289,7 +12180,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Fieber</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -12299,30 +12190,30 @@
         <v>5</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>Fatigue</t>
+          <t>Fieber</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12225,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Fieber</t>
+          <t>Halsschmerzen</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -12362,7 +12253,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>Fieber</t>
+          <t>Halsschmerz; Halsschmerzen</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -12379,7 +12270,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Halsschmerzen</t>
+          <t>Phosphat</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -12389,30 +12280,30 @@
         <v>5</v>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Halsschmerz; Halsschmerzen</t>
+          <t>Phospat</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12315,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Phosphat</t>
+          <t>Rückenschmerzenenenen</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -12434,30 +12325,30 @@
         <v>5</v>
       </c>
       <c r="E236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Phospat</t>
+          <t>Rückenschmer; Rückenschmerzen</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12360,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Rückenschmerzenenenen</t>
+          <t>Überforderung</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -12479,16 +12370,16 @@
         <v>5</v>
       </c>
       <c r="E237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H237" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -12497,12 +12388,12 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Rückenschmer; Rückenschmerzen</t>
+          <t>Überforderung</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -12514,35 +12405,35 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Überforderung</t>
+          <t>Allgemeinsymtomatik</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>Überforderung</t>
+          <t>Allgemeinsymtomatik</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -12559,7 +12450,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Allgemeinsymtomatik</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -12569,30 +12460,30 @@
         <v>4</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F239" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H239" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Allgemeinsymtomatik</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12495,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>Entfieberung</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -12614,25 +12505,25 @@
         <v>4</v>
       </c>
       <c r="E240" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G240" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>Entfieberung</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -12649,7 +12540,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Entfieberung</t>
+          <t>Hypotonie</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -12677,7 +12568,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Entfieberung</t>
+          <t>Hypotoni; Hypotonie</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -12694,7 +12585,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Hypotonie</t>
+          <t>Knieprobleme</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -12722,12 +12613,12 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Hypotoni; Hypotonie</t>
+          <t>Knieprobleme</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12630,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Knieprobleme</t>
+          <t>Kreislauf Zusammenbruch</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -12749,25 +12640,25 @@
         <v>4</v>
       </c>
       <c r="E243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F243" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H243" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Knieprobleme</t>
+          <t>Kreislauf Zusammenbruch</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -12784,7 +12675,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Kreislauf Zusammenbruch</t>
+          <t>Myoklonien</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -12794,25 +12685,25 @@
         <v>4</v>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>Kreislauf Zusammenbruch</t>
+          <t>Myoklonien</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -12829,7 +12720,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Myoklonien</t>
+          <t>Müdigkeit</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -12839,30 +12730,30 @@
         <v>4</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Myoklonien</t>
+          <t>Müdigkeit</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12765,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Müdigkeit</t>
+          <t>Oxycodonentzug</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -12884,30 +12775,30 @@
         <v>4</v>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Müdigkeit</t>
+          <t>Oxycodonentzug</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -12919,7 +12810,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Oxycodonentzug</t>
+          <t>Panik</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -12929,25 +12820,25 @@
         <v>4</v>
       </c>
       <c r="E247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>Oxycodonentzug</t>
+          <t>Panik</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -12964,7 +12855,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Panik</t>
+          <t>Systolikum</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -12974,25 +12865,25 @@
         <v>4</v>
       </c>
       <c r="E248" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F248" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H248" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Panik</t>
+          <t>Systolikum</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -13009,7 +12900,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Systolikum</t>
+          <t>Tagesmüdigkeit</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -13019,25 +12910,25 @@
         <v>4</v>
       </c>
       <c r="E249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G249" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Systolikum</t>
+          <t>Tagesmüdigkeit</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -13054,7 +12945,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Tagesmüdigkeit</t>
+          <t>Unsicherheiten</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -13082,7 +12973,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Tagesmüdigkeit</t>
+          <t>Unsicherheiten</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -13099,7 +12990,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Unsicherheiten</t>
+          <t>Zielkonflikt</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -13127,7 +13018,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Unsicherheiten</t>
+          <t>Zielkonflikt</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -13144,7 +13035,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Zielkonflikt</t>
+          <t>chronische</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -13154,30 +13045,30 @@
         <v>4</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F252" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H252" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>Zielkonflikt</t>
+          <t>chronische</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13080,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>chronische</t>
+          <t>dysurische Beschwerden</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -13199,30 +13090,30 @@
         <v>4</v>
       </c>
       <c r="E253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>chronische</t>
+          <t>dysurische Beschwerden</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13125,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>dysurische Beschwerden</t>
+          <t>lebensüberdrüssiger Gedanken</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -13262,7 +13153,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>dysurische Beschwerden</t>
+          <t>lebensüberdrüssiger Gedanken</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -13279,7 +13170,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>lebensüberdrüssiger Gedanken</t>
+          <t>thorakale Schmerzen</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -13307,7 +13198,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>lebensüberdrüssiger Gedanken</t>
+          <t>thorakale Schmerzen</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -13324,7 +13215,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>thorakale Schmerzen</t>
+          <t>Ösophagus</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -13352,12 +13243,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>thorakale Schmerzen</t>
+          <t>Ösophagus</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -13369,40 +13260,40 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Ösophagus</t>
+          <t>Aggression</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F257" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H257" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Ösophagus</t>
+          <t>Aggression; Aggressionen</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -13414,7 +13305,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Aggression</t>
+          <t>Atrophie</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -13424,30 +13315,30 @@
         <v>3</v>
       </c>
       <c r="E258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>Aggression; Aggressionen</t>
+          <t>Atrophie</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13350,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Atrophie</t>
+          <t>Blut</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -13469,30 +13360,30 @@
         <v>3</v>
       </c>
       <c r="E259" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>Atrophie</t>
+          <t>Blut</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13395,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Blut</t>
+          <t>Blutung</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -13514,16 +13405,16 @@
         <v>3</v>
       </c>
       <c r="E260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -13532,7 +13423,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Blut</t>
+          <t>Blutung</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -13549,7 +13440,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Blutung</t>
+          <t>Herzfrequenz (HF)</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -13577,12 +13468,12 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Blutung</t>
+          <t>HF</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -13594,7 +13485,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Herzfrequenz (HF)</t>
+          <t>Hilflosigkeit</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -13604,30 +13495,30 @@
         <v>3</v>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>HF</t>
+          <t>Hilflosigkeit</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13530,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Hilflosigkeit</t>
+          <t>Hustenreiz</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -13667,7 +13558,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Hilflosigkeit</t>
+          <t>Hustenreiz</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -13684,7 +13575,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Hustenreiz</t>
+          <t>Leucos</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -13694,25 +13585,25 @@
         <v>3</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Hustenreiz</t>
+          <t>Leucos</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -13729,7 +13620,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Leucos</t>
+          <t>Luftnot</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -13739,25 +13630,25 @@
         <v>3</v>
       </c>
       <c r="E265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H265" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>Leucos</t>
+          <t>Luftnot</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -13774,7 +13665,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Luftnot</t>
+          <t>Missempfindungen Oberbauch</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -13784,25 +13675,25 @@
         <v>3</v>
       </c>
       <c r="E266" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F266" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H266" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>Luftnot</t>
+          <t>Missempfindungen Oberbauch</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -13819,7 +13710,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Missempfindungen Oberbauch</t>
+          <t>Schnupfen</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -13829,25 +13720,25 @@
         <v>3</v>
       </c>
       <c r="E267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Missempfindungen Oberbauch</t>
+          <t>Schnupfen</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -13864,7 +13755,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Schnupfen</t>
+          <t>Therapiemotivation</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -13874,30 +13765,30 @@
         <v>3</v>
       </c>
       <c r="E268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Schnupfen</t>
+          <t>Therapiemotivation</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13800,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Therapiemotivation</t>
+          <t>Trauer</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -13919,30 +13810,30 @@
         <v>3</v>
       </c>
       <c r="E269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>Therapiemotivation</t>
+          <t>Trauer</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13845,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Trauer</t>
+          <t>Verzweiflung</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -13982,7 +13873,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>Trauer</t>
+          <t>Verzweiflung</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -13999,7 +13890,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Verzweiflung</t>
+          <t>angespannt</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -14027,12 +13918,12 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Verzweiflung</t>
+          <t>angespannt</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -14044,7 +13935,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>angespannt</t>
+          <t>belastenden Gedanken</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -14054,30 +13945,30 @@
         <v>3</v>
       </c>
       <c r="E272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>angespannt</t>
+          <t>belastenden Gedanken</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -14089,7 +13980,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>belastenden Gedanken</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -14099,30 +13990,30 @@
         <v>3</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F273" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>belastenden Gedanken</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14025,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>emotional</t>
+          <t>körperlichen Beschwerden</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -14144,30 +14035,30 @@
         <v>3</v>
       </c>
       <c r="E274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>emotional</t>
+          <t>körperlichen Beschwerden</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14070,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>körperlichen Beschwerden</t>
+          <t>müde</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -14189,30 +14080,30 @@
         <v>3</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H275" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>körperlichen Beschwerden</t>
+          <t>müde</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14115,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>müde</t>
+          <t>psychische</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -14234,25 +14125,25 @@
         <v>3</v>
       </c>
       <c r="E276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>müde</t>
+          <t>psychische</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -14269,7 +14160,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>psychische</t>
+          <t>richtig krank</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -14297,12 +14188,12 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>psychische</t>
+          <t>richtig krank</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14205,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>richtig krank</t>
+          <t>schwerhörig</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -14324,25 +14215,25 @@
         <v>3</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>richtig krank</t>
+          <t>schwerhörig</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -14359,7 +14250,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>schwerhörig</t>
+          <t>somatischen Beschwerden</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -14369,25 +14260,25 @@
         <v>3</v>
       </c>
       <c r="E279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>schwerhörig</t>
+          <t>somatischen Beschwerden</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -14404,7 +14295,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>somatischen Beschwerden</t>
+          <t>Ärger</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -14414,25 +14305,25 @@
         <v>3</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>somatischen Beschwerden</t>
+          <t>Ärger</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -14449,7 +14340,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Ärger</t>
+          <t>Überwältigung</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -14459,25 +14350,25 @@
         <v>3</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Ärger</t>
+          <t>Überwältigung</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -14489,45 +14380,45 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>symptom</t>
+          <t>therapy</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Überwältigung</t>
+          <t>Psychotherapie (PT)</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="D282" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="E282" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F282" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G282" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H282" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Überwältigung</t>
+          <t>CP; Einzelsitzungen; PT; Psychother; Psychotherapie; Pt; pt</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; humadex; medner</t>
         </is>
       </c>
     </row>
@@ -14539,26 +14430,26 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Psychotherapie (PT)</t>
+          <t>Gesprächstherapie</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D283" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E283" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F283" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G283" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H283" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -14567,12 +14458,12 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>CP; Einzelsitzungen; PT; Psychother; Psychotherapie; Pt; pt</t>
+          <t>GT; Gesprächsther; Gesprächstherap; Gesprächstherapie; gt</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>gliner; humadex; medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -14584,26 +14475,26 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Gesprächstherapie</t>
+          <t>Gruppentherapie</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D284" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E284" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F284" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G284" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H284" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -14612,7 +14503,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>GT; Gesprächsther; Gesprächstherap; Gesprächstherapie; gt</t>
+          <t>Gruppenther; Gruppentherapie; Gruppentherapien</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -14629,26 +14520,26 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Gruppentherapie</t>
+          <t>Therapie</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D285" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E285" t="n">
         <v>8</v>
       </c>
       <c r="F285" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G285" t="n">
         <v>8</v>
       </c>
       <c r="H285" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -14657,7 +14548,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Gruppenther; Gruppentherapie; Gruppentherapien</t>
+          <t>Therapie; Therapien</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -14674,26 +14565,26 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Therapie</t>
+          <t>Supervision</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D286" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E286" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F286" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G286" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H286" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -14702,12 +14593,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Therapie; Therapien</t>
+          <t>Supervision; pro</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex; medner</t>
         </is>
       </c>
     </row>
@@ -14719,26 +14610,26 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Supervision</t>
+          <t>Einzeltherapie (EG)</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D287" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E287" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F287" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G287" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H287" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -14747,12 +14638,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Supervision; pro</t>
+          <t>Bezugstherapie; Einzelgespräch; Einzelther; Einzeltherapie; bezugstherap; os</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>humadex; medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -14764,26 +14655,26 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Einzeltherapie (EG)</t>
+          <t>Kunsttherapie</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D288" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E288" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G288" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H288" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -14792,7 +14683,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Bezugstherapie; Einzelgespräch; Einzelther; Einzeltherapie; bezugstherap; os</t>
+          <t>Kunstther; Kunsttherapie</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -14809,7 +14700,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Kunsttherapie</t>
+          <t>Psychoedukation</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -14819,16 +14710,16 @@
         <v>11</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F289" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G289" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H289" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -14837,7 +14728,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Kunstther; Kunsttherapie</t>
+          <t>Diabetes; Psychoedukation</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -14854,27 +14745,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Psychoedukation</t>
+          <t>ambulante Psychotherapie (PT)</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D290" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E290" t="n">
+        <v>4</v>
+      </c>
+      <c r="F290" t="n">
         <v>6</v>
       </c>
-      <c r="F290" t="n">
-        <v>5</v>
-      </c>
       <c r="G290" t="n">
+        <v>4</v>
+      </c>
+      <c r="H290" t="n">
         <v>6</v>
       </c>
-      <c r="H290" t="n">
-        <v>5</v>
-      </c>
       <c r="I290" t="inlineStr">
         <is>
           <t>direct_and_group</t>
@@ -14882,7 +14773,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Diabetes; Psychoedukation</t>
+          <t>ambulante; ambulante PT; ambulante Psychotherapie; ambulante psychotherapeutische Unterstützung; ambulanter</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -14899,26 +14790,26 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ambulante Psychotherapie (PT)</t>
+          <t>SKID Diagnostik</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D291" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E291" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F291" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G291" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H291" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -14927,7 +14818,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>ambulante; ambulante PT; ambulante Psychotherapie; ambulante psychotherapeutische Unterstützung; ambulanter</t>
+          <t>SKID; SKID Diagnostik; SKID Interview</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -14944,26 +14835,26 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SKID Diagnostik</t>
+          <t>gelbe Karte</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D292" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E292" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G292" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -14972,12 +14863,12 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>SKID; SKID Diagnostik; SKID Interview</t>
+          <t>gelbe; gelbe Karte</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -14989,26 +14880,26 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>gelbe Karte</t>
+          <t>Antisuizidpakt</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D293" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E293" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G293" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H293" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -15017,12 +14908,12 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>gelbe; gelbe Karte</t>
+          <t>Antisuizidpakt</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -15034,7 +14925,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Antisuizidpakt</t>
+          <t>Krisenintervention</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -15044,30 +14935,30 @@
         <v>3</v>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>Antisuizidpakt</t>
+          <t>Krisenintervention</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -15079,7 +14970,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Krisenintervention</t>
+          <t>Krisenintervision</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -15089,25 +14980,25 @@
         <v>3</v>
       </c>
       <c r="E295" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G295" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Krisenintervention</t>
+          <t>Kriseninter</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -15124,7 +15015,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Krisenintervision</t>
+          <t>Probatorik</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -15134,25 +15025,25 @@
         <v>3</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H296" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>Kriseninter</t>
+          <t>Probatorik</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -15169,7 +15060,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Probatorik</t>
+          <t>Schmerzedukation</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -15179,25 +15070,25 @@
         <v>3</v>
       </c>
       <c r="E297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G297" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H297" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Probatorik</t>
+          <t>Schmerzeduka</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -15214,7 +15105,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Schmerzedukation</t>
+          <t>bezugstherapeutischen</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -15224,75 +15115,75 @@
         <v>3</v>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>Schmerzeduka</t>
+          <t>bezugstherapeutischen</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>therapy</t>
+          <t>treatment</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>bezugstherapeutischen</t>
+          <t>Visitendienst (VD)</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D299" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E299" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G299" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H299" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>bezugstherapeutischen</t>
+          <t>lo</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex; medner</t>
         </is>
       </c>
     </row>
@@ -15304,26 +15195,26 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Visitendienst (VD)</t>
+          <t>Dialyse</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D300" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E300" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F300" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G300" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H300" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -15332,12 +15223,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>lo</t>
+          <t>Dialyse</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>humadex; medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -15349,26 +15240,26 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Dialyse</t>
+          <t>Reha</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D301" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E301" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G301" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -15377,12 +15268,12 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Dialyse</t>
+          <t>Reha</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -15394,40 +15285,40 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Reha</t>
+          <t>Peritonealdialyse</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D302" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F302" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Reha</t>
+          <t>Peritonealdialyse; openem</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>gliner; medner</t>
         </is>
       </c>
     </row>
@@ -15439,40 +15330,40 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Peritonealdialyse</t>
+          <t>Ernährungsberatung</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D303" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E303" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F303" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H303" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Peritonealdialyse; openem</t>
+          <t>Ernährungsber; Ernährungsberatung</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>gliner; medner</t>
+          <t>gliner; humadex</t>
         </is>
       </c>
     </row>
@@ -15484,26 +15375,26 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ernährungsberatung</t>
+          <t>Intervallbehandlung</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D304" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E304" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -15512,7 +15403,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Ernährungsber; Ernährungsberatung</t>
+          <t>Intervallbehandlung; Intervalltherapie</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -15529,7 +15420,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Intervallbehandlung</t>
+          <t>Lehrküche</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -15539,16 +15430,16 @@
         <v>4</v>
       </c>
       <c r="E305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G305" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -15557,12 +15448,12 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Intervallbehandlung; Intervalltherapie</t>
+          <t>Lehrkü; Lehrküche</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>gliner; humadex</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15465,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Lehrküche</t>
+          <t>Physiotherapie</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -15584,16 +15475,16 @@
         <v>4</v>
       </c>
       <c r="E306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -15602,12 +15493,12 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Lehrkü; Lehrküche</t>
+          <t>Physiotherapie</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -15619,7 +15510,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Physiotherapie</t>
+          <t>Schmerzkonsil</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -15647,12 +15538,12 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Physiotherapie</t>
+          <t>Schmerzkon; Schmerzkonsil</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15555,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Schmerzkonsil</t>
+          <t>Sonde</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -15674,25 +15565,25 @@
         <v>4</v>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F308" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H308" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>Schmerzkon; Schmerzkonsil</t>
+          <t>Sonde</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -15709,7 +15600,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Sonde</t>
+          <t>Wärmflasche</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -15719,25 +15610,25 @@
         <v>4</v>
       </c>
       <c r="E309" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G309" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>Sonde</t>
+          <t>Wärmflasche</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -15754,26 +15645,26 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Wärmflasche</t>
+          <t>Allgemeinchirurgie</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E310" t="n">
         <v>0</v>
       </c>
       <c r="F310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
       </c>
       <c r="H310" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -15782,12 +15673,12 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Wärmflasche</t>
+          <t>Allgemeinchirurgie</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>humadex</t>
+          <t>gliner</t>
         </is>
       </c>
     </row>
@@ -15799,7 +15690,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Allgemeinchirurgie</t>
+          <t>Opioidreduktion</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -15809,30 +15700,30 @@
         <v>3</v>
       </c>
       <c r="E311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H311" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>group_only</t>
+          <t>direct_and_group</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Allgemeinchirurgie</t>
+          <t>Opioidreduktion</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>gliner</t>
+          <t>humadex</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15735,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Opioidreduktion</t>
+          <t>Reduktion</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -15854,25 +15745,25 @@
         <v>3</v>
       </c>
       <c r="E312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>direct_and_group</t>
+          <t>direct_only</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Opioidreduktion</t>
+          <t>Reduktion</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -15889,7 +15780,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Reduktion</t>
+          <t>Substitution</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -15899,73 +15790,28 @@
         <v>3</v>
       </c>
       <c r="E313" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G313" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>direct_only</t>
+          <t>group_only</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>Reduktion</t>
+          <t>Substitution</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
-        <is>
-          <t>humadex</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>treatment</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Substitution</t>
-        </is>
-      </c>
-      <c r="C314" t="n">
-        <v>3</v>
-      </c>
-      <c r="D314" t="n">
-        <v>3</v>
-      </c>
-      <c r="E314" t="n">
-        <v>0</v>
-      </c>
-      <c r="F314" t="n">
-        <v>3</v>
-      </c>
-      <c r="G314" t="n">
-        <v>0</v>
-      </c>
-      <c r="H314" t="n">
-        <v>3</v>
-      </c>
-      <c r="I314" t="inlineStr">
-        <is>
-          <t>group_only</t>
-        </is>
-      </c>
-      <c r="J314" t="inlineStr">
-        <is>
-          <t>Substitution</t>
-        </is>
-      </c>
-      <c r="K314" t="inlineStr">
         <is>
           <t>humadex</t>
         </is>
